--- a/excel-files/QUEZON CITY/SAN FRANCISCO ES.xlsx
+++ b/excel-files/QUEZON CITY/SAN FRANCISCO ES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29706"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="236" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31B2123E-A81F-42E6-B1E6-8686B2E5FE8A}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F148B9C4-111B-4765-9B28-92062AA5EB41}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5790,8 +5790,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5806,7 +5806,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14039,186 +14039,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C5:C12 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C127" name="Textbooks"/>
@@ -14236,11 +14056,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L4:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{FC26B654-7480-4D0F-A288-31EC569AE291}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14255,7 +14075,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -22790,186 +22610,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C91:C101 C103:C113 C115:C122" name="Textbooks"/>
@@ -22987,8 +22627,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/QUEZON CITY/SAN FRANCISCO ES.xlsx
+++ b/excel-files/QUEZON CITY/SAN FRANCISCO ES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10403"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F148B9C4-111B-4765-9B28-92062AA5EB41}"/>
+  <xr:revisionPtr revIDLastSave="301" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FD8ABA6-333E-9745-BFBA-06907E492953}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="93">
   <si>
     <t>Grade Level</t>
   </si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>Music and Arts</t>
-  </si>
-  <si>
-    <t>SDO</t>
   </si>
   <si>
     <t>VE</t>
@@ -312,12 +309,18 @@
   <si>
     <t>Arts</t>
   </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1829,13 +1832,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1859,6 +1855,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2937,13 +2940,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2980,6 +2976,13 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3022,7 +3025,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3041,7 +3044,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
@@ -3097,7 +3100,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
@@ -3470,17 +3473,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.0859375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3506,7 +3509,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3514,24 +3517,27 @@
         <v>8</v>
       </c>
       <c r="C2" s="1">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D2" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="5"/>
+        <v>409</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G2" s="3">
         <f>IF((C2-D2)&lt;0,0,C2-D2)</f>
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3539,24 +3545,27 @@
         <v>9</v>
       </c>
       <c r="C3" s="1">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D3" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="5"/>
+        <v>409</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G3" s="3">
         <f>IF((C3-D3)&lt;0,0,C3-D3)</f>
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3564,24 +3573,27 @@
         <v>10</v>
       </c>
       <c r="C4" s="1">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D4" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="5"/>
+        <v>409</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G4" s="3">
         <f>IF((C4-D4)&lt;0,0,C4-D4)</f>
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3589,24 +3601,27 @@
         <v>11</v>
       </c>
       <c r="C5" s="1">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D5" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
+        <v>409</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.5">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3614,29 +3629,26 @@
         <v>12</v>
       </c>
       <c r="C6" s="1">
-        <v>253</v>
-      </c>
-      <c r="D6" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="5"/>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>252</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3646,22 +3658,19 @@
       <c r="C8" s="1">
         <v>248</v>
       </c>
-      <c r="D8" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3">
         <f>IF((C8-D8)&lt;0,0,C8-D8)</f>
-        <v>48</v>
+        <v>248</v>
       </c>
       <c r="H8" s="4">
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3671,22 +3680,19 @@
       <c r="C9" s="1">
         <v>248</v>
       </c>
-      <c r="D9" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="5"/>
       <c r="G9" s="3">
         <f>IF((C9-D9)&lt;0,0,C9-D9)</f>
-        <v>48</v>
+        <v>248</v>
       </c>
       <c r="H9" s="4">
         <f>IF((D9-C9)&lt;0,0,D9-C9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3696,22 +3702,19 @@
       <c r="C10" s="1">
         <v>248</v>
       </c>
-      <c r="D10" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="5"/>
       <c r="G10" s="3">
         <f>IF((C10-D10)&lt;0,0,C10-D10)</f>
-        <v>48</v>
+        <v>248</v>
       </c>
       <c r="H10" s="4">
         <f>IF((D10-C10)&lt;0,0,D10-C10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3722,21 +3725,24 @@
         <v>248</v>
       </c>
       <c r="D11" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+        <v>300</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="19.5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3746,27 +3752,24 @@
       <c r="C12" s="1">
         <v>248</v>
       </c>
-      <c r="D12" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="5"/>
       <c r="G12" s="3">
         <f>IF((C12-D12)&lt;0,0,C12-D12)</f>
-        <v>48</v>
+        <v>248</v>
       </c>
       <c r="H12" s="4">
         <f>IF((D12-C12)&lt;0,0,D12-C12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3776,22 +3779,19 @@
       <c r="C14" s="1">
         <v>276</v>
       </c>
-      <c r="D14" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="5"/>
       <c r="G14" s="3">
         <f t="shared" ref="G14:G19" si="2">IF((C14-D14)&lt;0,0,C14-D14)</f>
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" ref="H14:H19" si="3">IF((D14-C14)&lt;0,0,D14-C14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3801,22 +3801,19 @@
       <c r="C15" s="1">
         <v>276</v>
       </c>
-      <c r="D15" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="5"/>
       <c r="G15" s="3">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3826,22 +3823,19 @@
       <c r="C16" s="1">
         <v>276</v>
       </c>
-      <c r="D16" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="5"/>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="H16" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3851,22 +3845,19 @@
       <c r="C17" s="1">
         <v>276</v>
       </c>
-      <c r="D17" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="5"/>
       <c r="G17" s="3">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="H17" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3876,22 +3867,19 @@
       <c r="C18" s="1">
         <v>276</v>
       </c>
-      <c r="D18" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="5"/>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.5">
+    <row r="19" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3901,22 +3889,19 @@
       <c r="C19" s="1">
         <v>276</v>
       </c>
-      <c r="D19" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="5"/>
       <c r="G19" s="3">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3926,7 +3911,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3936,22 +3921,19 @@
       <c r="C21" s="1">
         <v>321</v>
       </c>
-      <c r="D21" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>300</v>
-      </c>
+      <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="5"/>
       <c r="G21" s="3">
         <f t="shared" ref="G21:G29" si="4">IF((C21-D21)&lt;0,0,C21-D21)</f>
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3962,21 +3944,24 @@
         <v>321</v>
       </c>
       <c r="D22" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>300</v>
-      </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="5"/>
+        <v>375</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="19.5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3987,21 +3972,24 @@
         <v>321</v>
       </c>
       <c r="D23" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>300</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="5"/>
+        <v>375</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -4012,21 +4000,24 @@
         <v>321</v>
       </c>
       <c r="D24" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>300</v>
-      </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="5"/>
+        <v>375</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -4037,21 +4028,24 @@
         <v>321</v>
       </c>
       <c r="D25" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>300</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="5"/>
+        <v>375</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -4062,21 +4056,24 @@
         <v>321</v>
       </c>
       <c r="D26" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>300</v>
-      </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="5"/>
+        <v>375</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4087,21 +4084,24 @@
         <v>321</v>
       </c>
       <c r="D27" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>300</v>
-      </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="5"/>
+        <v>375</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4111,22 +4111,19 @@
       <c r="C28" s="1">
         <v>321</v>
       </c>
-      <c r="D28" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>300</v>
-      </c>
+      <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4137,21 +4134,24 @@
         <v>321</v>
       </c>
       <c r="D29" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>300</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+        <v>375</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4161,7 +4161,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4172,25 +4172,24 @@
         <v>269</v>
       </c>
       <c r="D31" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="E31" s="1">
         <v>2025</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4200,22 +4199,19 @@
       <c r="C32" s="1">
         <v>269</v>
       </c>
-      <c r="D32" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="5"/>
       <c r="G32" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>269</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4225,22 +4221,19 @@
       <c r="C33" s="1">
         <v>269</v>
       </c>
-      <c r="D33" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="5"/>
       <c r="G33" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>269</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4250,22 +4243,19 @@
       <c r="C34" s="1">
         <v>269</v>
       </c>
-      <c r="D34" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="5"/>
       <c r="G34" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>269</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4276,21 +4266,24 @@
         <v>269</v>
       </c>
       <c r="D35" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
-      <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
+        <v>325</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4301,25 +4294,24 @@
         <v>269</v>
       </c>
       <c r="D36" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="E36" s="1">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="27.75" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4330,25 +4322,24 @@
         <v>269</v>
       </c>
       <c r="D37" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="E37" s="1">
         <v>2025</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="27.75" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4359,21 +4350,24 @@
         <v>269</v>
       </c>
       <c r="D38" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+        <v>325</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="27.75" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4383,22 +4377,19 @@
       <c r="C39" s="1">
         <v>269</v>
       </c>
-      <c r="D39" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="5"/>
       <c r="G39" s="3">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>269</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4408,7 +4399,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4418,22 +4409,19 @@
       <c r="C41" s="1">
         <v>280</v>
       </c>
-      <c r="D41" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="5"/>
       <c r="G41" s="3">
         <f t="shared" ref="G41:G49" si="8">IF((C41-D41)&lt;0,0,C41-D41)</f>
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H41" s="4">
         <f t="shared" ref="H41:H49" si="9">IF((D41-C41)&lt;0,0,D41-C41)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4443,22 +4431,19 @@
       <c r="C42" s="1">
         <v>280</v>
       </c>
-      <c r="D42" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="5"/>
       <c r="G42" s="3">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4468,22 +4453,19 @@
       <c r="C43" s="1">
         <v>280</v>
       </c>
-      <c r="D43" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
       <c r="G43" s="3">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4493,22 +4475,19 @@
       <c r="C44" s="1">
         <v>280</v>
       </c>
-      <c r="D44" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="5"/>
       <c r="G44" s="3">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4518,22 +4497,19 @@
       <c r="C45" s="1">
         <v>280</v>
       </c>
-      <c r="D45" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="5"/>
       <c r="G45" s="3">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H45" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4543,22 +4519,19 @@
       <c r="C46" s="1">
         <v>280</v>
       </c>
-      <c r="D46" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="5"/>
       <c r="G46" s="3">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H46" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4568,22 +4541,19 @@
       <c r="C47" s="1">
         <v>280</v>
       </c>
-      <c r="D47" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="5"/>
       <c r="G47" s="3">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H47" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4593,22 +4563,19 @@
       <c r="C48" s="1">
         <v>280</v>
       </c>
-      <c r="D48" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="5"/>
       <c r="G48" s="3">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H48" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4618,22 +4585,19 @@
       <c r="C49" s="1">
         <v>280</v>
       </c>
-      <c r="D49" s="1">
-        <f>ROUNDDOWN(Table2[[#This Row],[Enrolment S.Y. 2025-2026 ]], -2)</f>
-        <v>200</v>
-      </c>
+      <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4643,7 +4607,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4668,7 +4632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -4693,7 +4657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4718,12 +4682,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>7</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C54" s="10">
         <v>0</v>
@@ -4743,7 +4707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1">
+    <row r="55" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4768,7 +4732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4793,7 +4757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4818,12 +4782,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>7</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C58" s="10">
         <v>0</v>
@@ -4843,7 +4807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -4868,7 +4832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4878,7 +4842,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4903,7 +4867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4928,7 +4892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4953,12 +4917,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>8</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C64" s="10">
         <v>0</v>
@@ -4978,12 +4942,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>8</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C65" s="10">
         <v>0</v>
@@ -5003,7 +4967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -5028,7 +4992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -5053,12 +5017,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>8</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C68" s="10">
         <v>0</v>
@@ -5078,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -5103,7 +5067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -5113,7 +5077,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -5138,7 +5102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -5163,7 +5127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -5188,12 +5152,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>9</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C74" s="10">
         <v>0</v>
@@ -5213,12 +5177,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>9</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C75" s="10">
         <v>0</v>
@@ -5238,7 +5202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -5263,7 +5227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -5288,12 +5252,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>9</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C78" s="10">
         <v>0</v>
@@ -5313,7 +5277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -5338,7 +5302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5348,7 +5312,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5373,7 +5337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5398,7 +5362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5423,12 +5387,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>10</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C84" s="10">
         <v>0</v>
@@ -5448,12 +5412,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>10</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C85" s="10">
         <v>0</v>
@@ -5473,7 +5437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5498,7 +5462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5523,12 +5487,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>10</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C88" s="10">
         <v>0</v>
@@ -5548,7 +5512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5573,7 +5537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5583,12 +5547,12 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1">
+    <row r="91" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B91" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>25</v>
       </c>
       <c r="C91" s="1">
         <v>0</v>
@@ -5608,12 +5572,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1">
+    <row r="92" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C92" s="1">
         <v>0</v>
@@ -5633,12 +5597,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1">
+    <row r="93" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C93" s="1">
         <v>0</v>
@@ -5658,12 +5622,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1">
+    <row r="94" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C94" s="1">
         <v>0</v>
@@ -5683,12 +5647,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1">
+    <row r="95" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
@@ -5708,12 +5672,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1">
+    <row r="96" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
@@ -5733,12 +5697,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1">
+    <row r="97" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C97" s="1">
         <v>0</v>
@@ -5758,12 +5722,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1">
+    <row r="98" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C98" s="1">
         <v>0</v>
@@ -5807,37 +5771,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
   <dimension ref="A1:AA127"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.5703125" customWidth="1"/>
-    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.5703125" customWidth="1"/>
-    <col min="14" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="33.42578125" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="35.51171875" customWidth="1"/>
+    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.609375" customWidth="1"/>
+    <col min="14" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="33.359375" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E1" s="42"/>
       <c r="F1" s="42"/>
@@ -5845,7 +5809,7 @@
       <c r="H1" s="42"/>
       <c r="I1" s="42"/>
       <c r="J1" s="43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K1" s="43"/>
       <c r="L1" s="43"/>
@@ -5853,7 +5817,7 @@
       <c r="N1" s="43"/>
       <c r="O1" s="43"/>
       <c r="P1" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="44"/>
       <c r="R1" s="44"/>
@@ -5861,7 +5825,7 @@
       <c r="T1" s="44"/>
       <c r="U1" s="44"/>
       <c r="V1" s="45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="W1" s="45"/>
       <c r="X1" s="45"/>
@@ -5869,7 +5833,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5880,81 +5844,81 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="G2" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="H2" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="I2" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="J2" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="K2" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="L2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="M2" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="O2" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="P2" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="Q2" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="R2" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="S2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="T2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="T2" s="17" t="s">
+      <c r="U2" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="U2" s="24" t="s">
+      <c r="V2" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="V2" s="26" t="s">
+      <c r="W2" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="X2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="Y2" s="41" t="s">
+      <c r="Z2" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="AA2" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="AA2" s="26" t="s">
+    </row>
+    <row r="3" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="39" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
-      <c r="A3" s="39" t="s">
-        <v>61</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="32">
@@ -6021,7 +5985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -6033,7 +5997,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="38.25">
+    <row r="5" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -6104,7 +6068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -6175,7 +6139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -6246,7 +6210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6317,7 +6281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6388,7 +6352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6459,7 +6423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.5">
+    <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6530,12 +6494,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.5">
+    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12" s="1">
         <v>253</v>
@@ -6601,7 +6565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6614,7 +6578,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6686,7 +6650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6758,7 +6722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6830,7 +6794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6902,7 +6866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6974,7 +6938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -7046,7 +7010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.5">
+    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -7118,12 +7082,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.5">
+    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C21" s="1">
         <f>TextBooks!$C$8</f>
@@ -7190,7 +7154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -7204,7 +7168,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="38.25">
+    <row r="23" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -7276,7 +7240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7348,7 +7312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7420,7 +7384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7492,7 +7456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7564,7 +7528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7636,7 +7600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7708,7 +7672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.5">
+    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7780,12 +7744,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.5">
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" s="1">
         <f>TextBooks!$C$14</f>
@@ -7852,7 +7816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7866,7 +7830,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.5">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7938,7 +7902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -8010,7 +7974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.5">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -8082,7 +8046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -8154,7 +8118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="38.25">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -8226,7 +8190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -8298,7 +8262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8370,7 +8334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8442,7 +8406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8514,7 +8478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8528,7 +8492,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8600,7 +8564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8672,7 +8636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8744,7 +8708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8816,7 +8780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8888,7 +8852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8960,7 +8924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -9032,7 +8996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -9104,7 +9068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -9176,7 +9140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -9190,7 +9154,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -9262,7 +9226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.5">
+    <row r="54" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -9334,7 +9298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9406,7 +9370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9478,7 +9442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="38.25">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9550,7 +9514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9622,7 +9586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.5">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9694,7 +9658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9766,7 +9730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9838,7 +9802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9852,7 +9816,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.5">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9923,7 +9887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.5">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9994,7 +9958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.5">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -10065,12 +10029,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.5">
+    <row r="66" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>7</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C66" s="10">
         <v>0</v>
@@ -10136,7 +10100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="38.25">
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -10207,7 +10171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.5">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -10278,7 +10242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.5">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -10349,12 +10313,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.5">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C70" s="10">
         <v>0</v>
@@ -10420,7 +10384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.5">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10491,7 +10455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C72" s="10">
         <v>0</v>
       </c>
@@ -10508,7 +10472,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.5">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10579,7 +10543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.5">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10650,7 +10614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.5">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10721,12 +10685,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.5">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>8</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C76" s="10">
         <v>0</v>
@@ -10792,12 +10756,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.5">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>8</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C77" s="10">
         <v>0</v>
@@ -10863,7 +10827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.5">
+    <row r="78" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10934,7 +10898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.5">
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -11005,12 +10969,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.5">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C80" s="10">
         <v>0</v>
@@ -11076,7 +11040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.5">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -11147,7 +11111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
@@ -11162,7 +11126,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.5">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -11233,7 +11197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.5">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -11304,7 +11268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.5">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -11375,12 +11339,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.5">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>9</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C86" s="10">
         <v>0</v>
@@ -11446,12 +11410,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.5">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>9</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C87" s="10">
         <v>0</v>
@@ -11517,7 +11481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.5">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11588,7 +11552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.5">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11659,12 +11623,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.5">
+    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>9</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C90" s="10">
         <v>0</v>
@@ -11730,7 +11694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.5">
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11801,7 +11765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
@@ -11816,7 +11780,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.5">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11887,7 +11851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.5">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11958,7 +11922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.5">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -12029,12 +11993,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.5">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>10</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C96" s="10">
         <v>0</v>
@@ -12100,12 +12064,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.5">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>10</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C97" s="10">
         <v>0</v>
@@ -12171,7 +12135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.5">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -12242,7 +12206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.5">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -12313,12 +12277,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.5">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>10</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C100" s="10">
         <v>0</v>
@@ -12384,7 +12348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.5">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12455,7 +12419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
@@ -12470,12 +12434,12 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.25">
+    <row r="103" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B103" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>25</v>
       </c>
       <c r="C103" s="5">
         <v>0</v>
@@ -12541,12 +12505,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.5">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C104" s="5">
         <v>0</v>
@@ -12612,12 +12576,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.5">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C105" s="5">
         <v>0</v>
@@ -12683,12 +12647,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.5">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C106" s="5">
         <v>0</v>
@@ -12754,12 +12718,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.25">
+    <row r="107" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C107" s="5">
         <v>0</v>
@@ -12825,12 +12789,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="38.25">
+    <row r="108" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C108" s="5">
         <v>0</v>
@@ -12896,12 +12860,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="57.75">
+    <row r="109" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C109" s="5">
         <v>0</v>
@@ -12967,12 +12931,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.25">
+    <row r="110" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C110" s="5">
         <v>0</v>
@@ -13038,7 +13002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="C111" s="13"/>
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
@@ -13050,7 +13014,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.5">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="5"/>
@@ -13112,7 +13076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.5">
+    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="5"/>
@@ -13174,7 +13138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.5">
+    <row r="114" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="5"/>
@@ -13236,7 +13200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.5">
+    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="5"/>
@@ -13298,7 +13262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.5">
+    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="5"/>
@@ -13360,7 +13324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.5">
+    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="5"/>
@@ -13422,7 +13386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.5">
+    <row r="118" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="5"/>
@@ -13484,7 +13448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.5">
+    <row r="119" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="5"/>
@@ -13546,7 +13510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.5">
+    <row r="120" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="5"/>
@@ -13608,7 +13572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.5">
+    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="5"/>
@@ -13670,7 +13634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.5">
+    <row r="122" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="5"/>
@@ -13732,7 +13696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.5">
+    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="5"/>
@@ -13794,7 +13758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.5">
+    <row r="124" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="5"/>
@@ -13856,7 +13820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.5">
+    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="5"/>
@@ -13918,7 +13882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.5">
+    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="5"/>
@@ -13980,7 +13944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.5">
+    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="5"/>
@@ -14076,37 +14040,37 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
   <dimension ref="A1:AB140"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="29.140625" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="16.41015625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="24.48046875" customWidth="1"/>
+    <col min="12" max="12" width="18.16015625" customWidth="1"/>
+    <col min="13" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="29.19140625" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="35"/>
       <c r="D1" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E1" s="42"/>
       <c r="F1" s="42"/>
@@ -14114,7 +14078,7 @@
       <c r="H1" s="42"/>
       <c r="I1" s="42"/>
       <c r="J1" s="43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K1" s="43"/>
       <c r="L1" s="43"/>
@@ -14122,7 +14086,7 @@
       <c r="N1" s="43"/>
       <c r="O1" s="43"/>
       <c r="P1" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="44"/>
       <c r="R1" s="44"/>
@@ -14130,7 +14094,7 @@
       <c r="T1" s="44"/>
       <c r="U1" s="44"/>
       <c r="V1" s="45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="W1" s="45"/>
       <c r="X1" s="45"/>
@@ -14138,7 +14102,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -14149,79 +14113,79 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="G2" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="H2" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="I2" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="J2" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="K2" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="L2" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="M2" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="O2" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="P2" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="Q2" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="R2" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="S2" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="T2" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="17" t="s">
+      <c r="U2" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="U2" s="24" t="s">
+      <c r="V2" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="V2" s="26" t="s">
+      <c r="W2" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="X2" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="Y2" s="41" t="s">
+      <c r="Z2" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="AA2" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="AA2" s="26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    </row>
+    <row r="3" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -14230,18 +14194,18 @@
       </c>
       <c r="C3" s="1">
         <f>TextBooks!$C$2</f>
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="1"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5">
         <f t="shared" ref="H3:H83" si="0">IF((D3-E3)&lt;0,0,(D3-E3))</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" ref="I3:I83" si="1">IF((E3-D3)&lt;0,0,(E3-D3))</f>
@@ -14249,14 +14213,14 @@
       </c>
       <c r="J3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
         <f t="shared" ref="N3:N72" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="O3" s="5">
         <f t="shared" ref="O3:O72" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
@@ -14264,14 +14228,14 @@
       </c>
       <c r="P3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="Q3" s="5"/>
       <c r="R3" s="1"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5">
         <f t="shared" ref="T3:T72" si="4">IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" ref="U3:U72" si="5">IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
@@ -14279,21 +14243,21 @@
       </c>
       <c r="V3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="W3" s="5"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5">
         <f t="shared" ref="Z3:Z72" si="6">IF((V3-W3)&lt;0,0,(V3-W3))</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="AA3" s="5">
         <f t="shared" ref="AA3:AA72" si="7">IF((W3-V3)&lt;0,0,(W3-V3))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.5">
+    <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14302,18 +14266,18 @@
       </c>
       <c r="C4" s="1">
         <f>TextBooks!$C$2</f>
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="1"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5">
         <f t="shared" si="0"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="1"/>
@@ -14321,14 +14285,14 @@
       </c>
       <c r="J4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="1"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5">
         <f t="shared" si="2"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="O4" s="5">
         <f t="shared" si="3"/>
@@ -14336,14 +14300,14 @@
       </c>
       <c r="P4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="1"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5">
         <f t="shared" si="4"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="5"/>
@@ -14351,21 +14315,21 @@
       </c>
       <c r="V4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="W4" s="5"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="5"/>
       <c r="Z4" s="5">
         <f t="shared" si="6"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="AA4" s="5">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.5">
+    <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14374,18 +14338,18 @@
       </c>
       <c r="C5" s="1">
         <f>TextBooks!$C$2</f>
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="1"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
         <f t="shared" si="0"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="1"/>
@@ -14393,14 +14357,14 @@
       </c>
       <c r="J5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
         <f t="shared" si="2"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="O5" s="5">
         <f t="shared" si="3"/>
@@ -14408,14 +14372,14 @@
       </c>
       <c r="P5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
         <f t="shared" si="4"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="5"/>
@@ -14423,21 +14387,21 @@
       </c>
       <c r="V5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="W5" s="5"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
         <f t="shared" si="6"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="AA5" s="5">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14446,18 +14410,18 @@
       </c>
       <c r="C6" s="1">
         <f>TextBooks!$C$2</f>
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="1"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
         <f t="shared" si="0"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="1"/>
@@ -14465,14 +14429,14 @@
       </c>
       <c r="J6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
         <f t="shared" si="2"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="O6" s="5">
         <f t="shared" si="3"/>
@@ -14480,14 +14444,14 @@
       </c>
       <c r="P6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
         <f t="shared" si="4"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="5"/>
@@ -14495,21 +14459,21 @@
       </c>
       <c r="V6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
         <f t="shared" si="6"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14518,18 +14482,18 @@
       </c>
       <c r="C7" s="1">
         <f>TextBooks!$C$2</f>
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="1"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
         <f t="shared" si="0"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="1"/>
@@ -14537,14 +14501,14 @@
       </c>
       <c r="J7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
         <f t="shared" si="2"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="O7" s="5">
         <f t="shared" si="3"/>
@@ -14552,14 +14516,14 @@
       </c>
       <c r="P7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
         <f t="shared" si="4"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="5"/>
@@ -14567,21 +14531,21 @@
       </c>
       <c r="V7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="W7" s="5"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
         <f t="shared" si="6"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="AA7" s="5">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14590,18 +14554,18 @@
       </c>
       <c r="C8" s="1">
         <f>TextBooks!$C$2</f>
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="1"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
         <f>IF((D8-E8)&lt;0,0,(D8-E8))</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="I8" s="5">
         <f>IF((E8-D8)&lt;0,0,(E8-D8))</f>
@@ -14609,14 +14573,14 @@
       </c>
       <c r="J8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
         <f t="shared" si="2"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="O8" s="5">
         <f t="shared" si="3"/>
@@ -14624,14 +14588,14 @@
       </c>
       <c r="P8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
         <f t="shared" si="4"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="5"/>
@@ -14639,21 +14603,21 @@
       </c>
       <c r="V8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
         <f t="shared" si="6"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14662,18 +14626,18 @@
       </c>
       <c r="C9" s="1">
         <f>TextBooks!$C$2</f>
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
         <f>IF((D9-E9)&lt;0,0,(D9-E9))</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="I9" s="5">
         <f>IF((E9-D9)&lt;0,0,(E9-D9))</f>
@@ -14681,14 +14645,14 @@
       </c>
       <c r="J9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
         <f t="shared" si="2"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="3"/>
@@ -14696,14 +14660,14 @@
       </c>
       <c r="P9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
         <f t="shared" si="4"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="5"/>
@@ -14711,41 +14675,41 @@
       </c>
       <c r="V9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="W9" s="5"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
         <f t="shared" si="6"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="AA9" s="5">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1">
         <f>TextBooks!$C$2</f>
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
         <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="I10" s="5">
         <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
@@ -14753,14 +14717,14 @@
       </c>
       <c r="J10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="2"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="O10" s="5">
         <f t="shared" si="3"/>
@@ -14768,14 +14732,14 @@
       </c>
       <c r="P10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <f t="shared" si="4"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="5"/>
@@ -14783,22 +14747,22 @@
       </c>
       <c r="V10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="W10" s="5"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
         <f t="shared" si="6"/>
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="AA10" s="5">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14870,7 +14834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.5">
+    <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14942,7 +14906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.5">
+    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -15014,7 +14978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -15086,7 +15050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -15158,7 +15122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -15230,7 +15194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -15302,12 +15266,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="1">
         <f>TextBooks!$C$8</f>
@@ -15374,8 +15338,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15447,7 +15411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.5">
+    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15519,7 +15483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.5">
+    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15591,7 +15555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15663,7 +15627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15735,7 +15699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15807,7 +15771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15879,7 +15843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15951,12 +15915,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" s="1">
         <f>TextBooks!$C$14</f>
@@ -16023,8 +15987,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -16096,7 +16060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.5">
+    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -16168,7 +16132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.5">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -16240,7 +16204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -16312,7 +16276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="38.25">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -16384,7 +16348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16456,12 +16420,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.5">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" s="1">
         <f>TextBooks!$C$21</f>
@@ -16528,12 +16492,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C38" s="1">
         <f>TextBooks!$C$21</f>
@@ -16600,7 +16564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16672,12 +16636,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C40" s="1">
         <f>TextBooks!$C$21</f>
@@ -16744,12 +16708,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C41" s="1">
         <f>TextBooks!$C$21</f>
@@ -16816,8 +16780,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16889,7 +16853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16961,7 +16925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -17033,7 +16997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -17105,7 +17069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -17177,7 +17141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -17249,12 +17213,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C49" s="1">
         <f>TextBooks!$C$31</f>
@@ -17321,12 +17285,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C50" s="1">
         <f>TextBooks!$C$31</f>
@@ -17393,7 +17357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -17465,12 +17429,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.5">
+    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C52" s="1">
         <f>TextBooks!$C$31</f>
@@ -17537,12 +17501,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C53" s="1">
         <f>TextBooks!$C$31</f>
@@ -17609,8 +17573,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17682,7 +17646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17754,7 +17718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.5">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17826,7 +17790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17898,7 +17862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="38.25">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17970,7 +17934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -18042,12 +18006,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C61" s="1">
         <f>TextBooks!$C$41</f>
@@ -18114,12 +18078,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.5">
+    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C62" s="1">
         <f>TextBooks!$C$41</f>
@@ -18186,7 +18150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.5">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -18258,12 +18222,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.5">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C64" s="1">
         <f>TextBooks!$C$41</f>
@@ -18330,12 +18294,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.5">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C65" s="1">
         <f>TextBooks!$C$41</f>
@@ -18402,8 +18366,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.5">
+    <row r="66" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -18474,7 +18438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.5">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18545,7 +18509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.5">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18616,12 +18580,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.5">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C70" s="10">
         <v>0</v>
@@ -18687,7 +18651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="38.25">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18758,7 +18722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.5">
+    <row r="72" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18829,12 +18793,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.5">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="38">
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C73" s="10">
         <v>0</v>
@@ -18900,12 +18864,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.5">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C74" s="10">
         <v>0</v>
@@ -18971,12 +18935,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.5">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C75" s="10">
         <v>0</v>
@@ -19042,12 +19006,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.5">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="38">
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C76" s="10">
         <v>0</v>
@@ -19113,12 +19077,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.5">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C77" s="10">
         <v>0</v>
@@ -19184,8 +19148,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.5">
+    <row r="78" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -19256,7 +19220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.5">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -19327,7 +19291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.5">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -19398,12 +19362,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.5">
+    <row r="82" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C82" s="10">
         <v>0</v>
@@ -19469,12 +19433,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.5">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C83" s="10">
         <v>0</v>
@@ -19540,7 +19504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.5">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19611,12 +19575,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.5">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="38">
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C85" s="10">
         <v>0</v>
@@ -19682,12 +19646,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.5">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C86" s="10">
         <v>0</v>
@@ -19753,12 +19717,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.5">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C87" s="10">
         <v>0</v>
@@ -19824,12 +19788,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.5">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="38">
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C88" s="10">
         <v>0</v>
@@ -19895,12 +19859,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.5">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C89" s="10">
         <v>0</v>
@@ -19966,8 +19930,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1" ht="15"/>
-    <row r="91" spans="1:27" ht="19.5">
+    <row r="90" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -20038,7 +20002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.5">
+    <row r="92" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -20109,7 +20073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.5">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -20180,12 +20144,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.5">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C94" s="10">
         <v>0</v>
@@ -20251,12 +20215,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.5">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C95" s="10">
         <v>0</v>
@@ -20322,7 +20286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.5">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -20393,12 +20357,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.5">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="38">
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C97" s="10">
         <v>0</v>
@@ -20464,12 +20428,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.5">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C98" s="10">
         <v>0</v>
@@ -20535,12 +20499,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.5">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C99" s="10">
         <v>0</v>
@@ -20606,12 +20570,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.5">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="38">
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C100" s="10">
         <v>0</v>
@@ -20677,12 +20641,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.5">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C101" s="10">
         <v>0</v>
@@ -20748,8 +20712,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.5">
+    <row r="102" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20820,7 +20784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.5">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20891,7 +20855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.5">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20962,12 +20926,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.5">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C106" s="10">
         <v>0</v>
@@ -21033,12 +20997,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.5">
+    <row r="107" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C107" s="10">
         <v>0</v>
@@ -21104,7 +21068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.5">
+    <row r="108" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -21175,12 +21139,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.5">
+    <row r="109" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A109" s="38">
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C109" s="10">
         <v>0</v>
@@ -21246,12 +21210,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.5">
+    <row r="110" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C110" s="10">
         <v>0</v>
@@ -21317,12 +21281,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.5">
+    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C111" s="10">
         <v>0</v>
@@ -21388,12 +21352,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.5">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="38">
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C112" s="10">
         <v>0</v>
@@ -21459,12 +21423,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.5">
+    <row r="113" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C113" s="10">
         <v>0</v>
@@ -21530,13 +21494,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.25">
+    <row r="114" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="115" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B115" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>25</v>
       </c>
       <c r="C115" s="1">
         <v>0</v>
@@ -21602,12 +21566,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.5">
+    <row r="116" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C116" s="1">
         <v>0</v>
@@ -21673,12 +21637,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.5">
+    <row r="117" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C117" s="1">
         <v>0</v>
@@ -21744,12 +21708,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.5">
+    <row r="118" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C118" s="1">
         <v>0</v>
@@ -21815,12 +21779,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.25">
+    <row r="119" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C119" s="1">
         <v>0</v>
@@ -21886,12 +21850,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="38.25">
+    <row r="120" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C120" s="1">
         <v>0</v>
@@ -21957,12 +21921,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="57.75">
+    <row r="121" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C121" s="1">
         <v>0</v>
@@ -22028,12 +21992,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.25">
+    <row r="122" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C122" s="1">
         <v>0</v>
@@ -22099,8 +22063,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1"/>
-    <row r="124" spans="1:28">
+    <row r="123" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -22130,7 +22094,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -22160,7 +22124,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -22190,7 +22154,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -22220,7 +22184,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -22250,7 +22214,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -22280,7 +22244,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -22310,7 +22274,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -22340,7 +22304,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -22370,7 +22334,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -22400,7 +22364,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -22430,7 +22394,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -22460,7 +22424,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -22490,7 +22454,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -22520,7 +22484,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -22550,7 +22514,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -22580,7 +22544,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
